--- a/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03645999999999999</v>
+        <v>0.036235</v>
       </c>
       <c r="E2">
-        <v>0.07921</v>
+        <v>0.05606</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.000500530584276564</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.000500530584276564</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.0014316486144155</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.001215847086003445</v>
       </c>
       <c r="K2">
-        <v>4150.1</v>
+        <v>3315.72</v>
       </c>
       <c r="L2">
-        <v>0.3807081919089992</v>
+        <v>0.3623622857854779</v>
       </c>
       <c r="M2">
-        <v>403.11</v>
+        <v>8933.34</v>
       </c>
       <c r="N2">
-        <v>0.00829070850789459</v>
+        <v>0.2253424277433318</v>
       </c>
       <c r="O2">
-        <v>0.09713259921447676</v>
+        <v>2.694238355470305</v>
       </c>
       <c r="P2">
-        <v>395</v>
+        <v>5513.1</v>
       </c>
       <c r="Q2">
-        <v>0.00812391124164214</v>
+        <v>0.1390672848443877</v>
       </c>
       <c r="R2">
-        <v>0.09517842943543528</v>
+        <v>1.662715790235605</v>
       </c>
       <c r="S2">
-        <v>8.110000000000014</v>
+        <v>3420.239999999999</v>
       </c>
       <c r="T2">
-        <v>0.02011857805561761</v>
+        <v>0.3828624008489545</v>
       </c>
       <c r="U2">
-        <v>92126.90000000001</v>
+        <v>72620.10000000001</v>
       </c>
       <c r="V2">
-        <v>1.894761414095295</v>
+        <v>1.831833293814355</v>
       </c>
       <c r="W2">
-        <v>0.1271161727602344</v>
+        <v>0.07749163564393761</v>
       </c>
       <c r="X2">
-        <v>0.1461779924836601</v>
+        <v>0.2082037221441219</v>
       </c>
       <c r="Y2">
-        <v>-0.01906181972342572</v>
+        <v>-0.1307120865001843</v>
       </c>
       <c r="Z2">
-        <v>0.04263984488343375</v>
+        <v>0.03813411162796822</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04469212145394612</v>
+        <v>0.07143053677294475</v>
       </c>
       <c r="AC2">
-        <v>-0.04469212145394612</v>
+        <v>-0.07143053677294475</v>
       </c>
       <c r="AD2">
-        <v>289238.5</v>
+        <v>235059.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>289238.5</v>
+        <v>235059.2</v>
       </c>
       <c r="AG2">
-        <v>197111.6</v>
+        <v>162439.1</v>
       </c>
       <c r="AH2">
-        <v>0.8560887869664512</v>
+        <v>0.855686112909015</v>
       </c>
       <c r="AI2">
-        <v>0.8710318667293855</v>
+        <v>0.8842812509992684</v>
       </c>
       <c r="AJ2">
-        <v>0.8021356469508635</v>
+        <v>0.8038256652604753</v>
       </c>
       <c r="AK2">
-        <v>0.8215129535924593</v>
+        <v>0.8407847022299242</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-4.186999999999999</v>
+      </c>
+      <c r="AN2">
+        <v>-18221.64341085271</v>
+      </c>
+      <c r="AO2">
+        <v>-21.37030995106036</v>
+      </c>
+      <c r="AP2">
+        <v>-12592.17829457364</v>
+      </c>
+      <c r="AQ2">
+        <v>3.128731788870313</v>
       </c>
     </row>
     <row r="3">
@@ -710,10 +722,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00138</v>
+        <v>-0.00243</v>
       </c>
       <c r="E3">
-        <v>0.00142</v>
+        <v>-0.008880000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4101.8</v>
+        <v>3288.9</v>
       </c>
       <c r="L3">
-        <v>0.3831381120514114</v>
+        <v>0.3665983012684754</v>
       </c>
       <c r="M3">
-        <v>366.21</v>
+        <v>8898.799999999999</v>
       </c>
       <c r="N3">
-        <v>0.00762026243617008</v>
+        <v>0.2281199611374723</v>
       </c>
       <c r="O3">
-        <v>0.08928031595884733</v>
+        <v>2.705707075313935</v>
       </c>
       <c r="P3">
-        <v>358.1</v>
+        <v>5481.5</v>
       </c>
       <c r="Q3">
-        <v>0.007451505907518925</v>
+        <v>0.1405177739667207</v>
       </c>
       <c r="R3">
-        <v>0.08730313520893267</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S3">
-        <v>8.110000000000014</v>
+        <v>3417.299999999999</v>
       </c>
       <c r="T3">
-        <v>0.0221457633598209</v>
+        <v>0.3840180698521148</v>
       </c>
       <c r="U3">
-        <v>91171.8</v>
+        <v>71926.8</v>
       </c>
       <c r="V3">
-        <v>1.897143832167367</v>
+        <v>1.843837238812283</v>
       </c>
       <c r="W3">
-        <v>0.1073345353014908</v>
+        <v>0.07749163564393761</v>
       </c>
       <c r="X3">
-        <v>0.1650372122733927</v>
+        <v>0.2082037221441219</v>
       </c>
       <c r="Y3">
-        <v>-0.05770267697190187</v>
+        <v>-0.1307120865001843</v>
       </c>
       <c r="Z3">
-        <v>0.04218204971711967</v>
+        <v>0.03766900119245561</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04250696456949338</v>
+        <v>0.06688928287667767</v>
       </c>
       <c r="AC3">
-        <v>-0.04250696456949338</v>
+        <v>-0.06688928287667767</v>
       </c>
       <c r="AD3">
-        <v>286893.8</v>
+        <v>233408.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>286893.8</v>
+        <v>233408.5</v>
       </c>
       <c r="AG3">
-        <v>195722</v>
+        <v>161481.7</v>
       </c>
       <c r="AH3">
-        <v>0.8565241742677738</v>
+        <v>0.8568034100561711</v>
       </c>
       <c r="AI3">
-        <v>0.8711007228561547</v>
+        <v>0.8846857527950542</v>
       </c>
       <c r="AJ3">
-        <v>0.8028652133855445</v>
+        <v>0.8054311664862762</v>
       </c>
       <c r="AK3">
-        <v>0.8217588364833347</v>
+        <v>0.8414655561883908</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07429999999999999</v>
+        <v>0.07490000000000001</v>
       </c>
       <c r="E4">
-        <v>0.157</v>
+        <v>0.121</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,91 +862,216 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>48.3</v>
+        <v>35.4</v>
       </c>
       <c r="L4">
-        <v>0.2474385245901639</v>
+        <v>0.2054556006964596</v>
       </c>
       <c r="M4">
-        <v>36.9</v>
+        <v>34.54</v>
       </c>
       <c r="N4">
-        <v>0.06536758193091231</v>
+        <v>0.05758586195398466</v>
       </c>
       <c r="O4">
-        <v>0.7639751552795031</v>
+        <v>0.9757062146892655</v>
       </c>
       <c r="P4">
-        <v>36.9</v>
+        <v>31.6</v>
       </c>
       <c r="Q4">
-        <v>0.06536758193091231</v>
+        <v>0.05268422807602535</v>
       </c>
       <c r="R4">
-        <v>0.7639751552795031</v>
+        <v>0.8926553672316385</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.939999999999998</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.0851187029530978</v>
       </c>
       <c r="U4">
-        <v>955.1</v>
+        <v>552.3</v>
       </c>
       <c r="V4">
-        <v>1.691939769707706</v>
+        <v>0.9208069356452151</v>
       </c>
       <c r="W4">
-        <v>0.1468978102189781</v>
+        <v>0.09485530546623794</v>
       </c>
       <c r="X4">
-        <v>0.1273187726939277</v>
+        <v>0.1233984439245765</v>
       </c>
       <c r="Y4">
-        <v>0.01957903752505041</v>
+        <v>-0.02854313845833853</v>
       </c>
       <c r="Z4">
-        <v>0.1053426875337291</v>
+        <v>0.09774222827320174</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04687727833839886</v>
+        <v>0.07143053677294475</v>
       </c>
       <c r="AC4">
-        <v>-0.04687727833839886</v>
+        <v>-0.07143053677294475</v>
       </c>
       <c r="AD4">
-        <v>2344.7</v>
+        <v>1416.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2344.7</v>
+        <v>1416.9</v>
       </c>
       <c r="AG4">
-        <v>1389.6</v>
+        <v>864.6000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.8059604014849443</v>
+        <v>0.7025834283730847</v>
       </c>
       <c r="AI4">
-        <v>0.8626881047867839</v>
+        <v>0.822440213605758</v>
       </c>
       <c r="AJ4">
-        <v>0.7111202087917712</v>
+        <v>0.5904124556132205</v>
       </c>
       <c r="AK4">
-        <v>0.788291354663036</v>
+        <v>0.7386586928662966</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fellow Pankki Oyj (HLSE:FELLOW)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-0.6949924127465857</v>
+      </c>
+      <c r="H5">
+        <v>-0.6949924127465857</v>
+      </c>
+      <c r="I5">
+        <v>-1.987860394537178</v>
+      </c>
+      <c r="J5">
+        <v>-1.987860394537178</v>
+      </c>
+      <c r="K5">
+        <v>-8.58</v>
+      </c>
+      <c r="L5">
+        <v>-1.301972685887709</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>141</v>
+      </c>
+      <c r="V5">
+        <v>4.110787172011662</v>
+      </c>
+      <c r="W5">
+        <v>-0.5329192546583851</v>
+      </c>
+      <c r="X5">
+        <v>0.2277104026362627</v>
+      </c>
+      <c r="Y5">
+        <v>-0.7606296572946478</v>
+      </c>
+      <c r="Z5">
+        <v>0.2809036658141517</v>
+      </c>
+      <c r="AA5">
+        <v>-0.5583972719522591</v>
+      </c>
+      <c r="AB5">
+        <v>0.07356561526529523</v>
+      </c>
+      <c r="AC5">
+        <v>-0.6319628872175543</v>
+      </c>
+      <c r="AD5">
+        <v>233.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>233.8</v>
+      </c>
+      <c r="AG5">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.8720626631853785</v>
+      </c>
+      <c r="AI5">
+        <v>0.8835978835978836</v>
+      </c>
+      <c r="AJ5">
+        <v>0.7301337529504328</v>
+      </c>
+      <c r="AK5">
+        <v>0.7508090614886732</v>
+      </c>
+      <c r="AL5">
+        <v>0.613</v>
+      </c>
+      <c r="AM5">
+        <v>-4.186999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>-18.12403100775194</v>
+      </c>
+      <c r="AO5">
+        <v>-21.37030995106036</v>
+      </c>
+      <c r="AP5">
+        <v>-7.193798449612403</v>
+      </c>
+      <c r="AQ5">
+        <v>3.128731788870313</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.036235</v>
+        <v>0.0819</v>
       </c>
       <c r="E2">
-        <v>0.05606</v>
+        <v>0.1167</v>
+      </c>
+      <c r="F2">
+        <v>0.116</v>
       </c>
       <c r="G2">
-        <v>-0.000500530584276564</v>
+        <v>-0.0005542860769938747</v>
       </c>
       <c r="H2">
-        <v>-0.000500530584276564</v>
+        <v>-0.0005990351962931225</v>
       </c>
       <c r="I2">
-        <v>-0.0014316486144155</v>
+        <v>0.0001031451331365642</v>
       </c>
       <c r="J2">
-        <v>-0.001215847086003445</v>
+        <v>8.827321278215912e-05</v>
       </c>
       <c r="K2">
-        <v>3315.72</v>
+        <v>5447</v>
       </c>
       <c r="L2">
-        <v>0.3623622857854779</v>
+        <v>0.4321781078422038</v>
       </c>
       <c r="M2">
-        <v>8933.34</v>
+        <v>4693.2</v>
       </c>
       <c r="N2">
-        <v>0.2253424277433318</v>
+        <v>0.1064290087761072</v>
       </c>
       <c r="O2">
-        <v>2.694238355470305</v>
+        <v>0.8616118964567652</v>
       </c>
       <c r="P2">
-        <v>5513.1</v>
+        <v>3099.1</v>
       </c>
       <c r="Q2">
-        <v>0.1390672848443877</v>
+        <v>0.07027915731228881</v>
       </c>
       <c r="R2">
-        <v>1.662715790235605</v>
+        <v>0.5689553882871305</v>
       </c>
       <c r="S2">
-        <v>3420.239999999999</v>
+        <v>1594.1</v>
       </c>
       <c r="T2">
-        <v>0.3828624008489545</v>
+        <v>0.3396616381147192</v>
       </c>
       <c r="U2">
-        <v>72620.10000000001</v>
+        <v>64438.5</v>
       </c>
       <c r="V2">
-        <v>1.831833293814355</v>
+        <v>1.461289883665555</v>
       </c>
       <c r="W2">
-        <v>0.07749163564393761</v>
+        <v>0.1425302386400785</v>
       </c>
       <c r="X2">
-        <v>0.2082037221441219</v>
+        <v>0.1508060465346924</v>
       </c>
       <c r="Y2">
-        <v>-0.1307120865001843</v>
+        <v>-0.008275807894613962</v>
       </c>
       <c r="Z2">
-        <v>0.03813411162796822</v>
+        <v>0.06587871053855517</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07143053677294475</v>
+        <v>0.06041816179158038</v>
       </c>
       <c r="AC2">
-        <v>-0.07143053677294475</v>
+        <v>-0.05736554434814577</v>
       </c>
       <c r="AD2">
-        <v>235059.2</v>
+        <v>245868.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>235059.2</v>
+        <v>245868.1</v>
       </c>
       <c r="AG2">
-        <v>162439.1</v>
+        <v>181429.6</v>
       </c>
       <c r="AH2">
-        <v>0.855686112909015</v>
+        <v>0.8479230776393436</v>
       </c>
       <c r="AI2">
-        <v>0.8842812509992684</v>
+        <v>0.8832208299042269</v>
       </c>
       <c r="AJ2">
-        <v>0.8038256652604753</v>
+        <v>0.8044709581929582</v>
       </c>
       <c r="AK2">
-        <v>0.8407847022299242</v>
+        <v>0.8480467723856703</v>
       </c>
       <c r="AL2">
-        <v>0.613</v>
+        <v>3.39</v>
       </c>
       <c r="AM2">
-        <v>-4.186999999999999</v>
+        <v>3.39</v>
       </c>
       <c r="AN2">
-        <v>-18221.64341085271</v>
+        <v>127392.7979274611</v>
       </c>
       <c r="AO2">
-        <v>-21.37030995106036</v>
+        <v>0.3834808259587021</v>
       </c>
       <c r="AP2">
-        <v>-12592.17829457364</v>
+        <v>94004.97409326426</v>
       </c>
       <c r="AQ2">
-        <v>3.128731788870313</v>
+        <v>0.3834808259587021</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nordea Bank Abp (OM:NDA SE)</t>
+          <t>Alisa Pankki Oyj (HLSE:ALISA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,109 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00243</v>
-      </c>
-      <c r="E3">
-        <v>-0.008880000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-0.3234259259259259</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-0.349537037037037</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.06018518518518518</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.06018518518518518</v>
       </c>
       <c r="K3">
-        <v>3288.9</v>
+        <v>-4.1</v>
       </c>
       <c r="L3">
-        <v>0.3665983012684754</v>
+        <v>-0.1898148148148148</v>
       </c>
       <c r="M3">
-        <v>8898.799999999999</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.2281199611374723</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>2.705707075313935</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>5481.5</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1405177739667207</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>3417.299999999999</v>
-      </c>
-      <c r="T3">
-        <v>0.3840180698521148</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>71926.8</v>
+        <v>117.6</v>
       </c>
       <c r="V3">
-        <v>1.843837238812283</v>
+        <v>6.999999999999999</v>
       </c>
       <c r="W3">
-        <v>0.07749163564393761</v>
+        <v>-0.1331168831168831</v>
       </c>
       <c r="X3">
-        <v>0.2082037221441219</v>
+        <v>0.322664595466133</v>
       </c>
       <c r="Y3">
-        <v>-0.1307120865001843</v>
+        <v>-0.4557814785830161</v>
       </c>
       <c r="Z3">
-        <v>0.03766900119245561</v>
+        <v>0.1842688960928169</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.01109025763521583</v>
       </c>
       <c r="AB3">
-        <v>0.06688928287667767</v>
+        <v>0.06041816179158038</v>
       </c>
       <c r="AC3">
-        <v>-0.06688928287667767</v>
+        <v>-0.04932790415636455</v>
       </c>
       <c r="AD3">
-        <v>233408.5</v>
+        <v>271.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>233408.5</v>
+        <v>271.1</v>
       </c>
       <c r="AG3">
-        <v>161481.7</v>
+        <v>153.5</v>
       </c>
       <c r="AH3">
-        <v>0.8568034100561711</v>
+        <v>0.9416464050017367</v>
       </c>
       <c r="AI3">
-        <v>0.8846857527950542</v>
+        <v>0.9042695130086725</v>
       </c>
       <c r="AJ3">
-        <v>0.8054311664862762</v>
+        <v>0.9013505578391074</v>
       </c>
       <c r="AK3">
-        <v>0.8414655561883908</v>
+        <v>0.8424807903402854</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>3.39</v>
+      </c>
+      <c r="AN3">
+        <v>140.4663212435233</v>
+      </c>
+      <c r="AO3">
+        <v>0.3834808259587021</v>
+      </c>
+      <c r="AP3">
+        <v>79.5336787564767</v>
+      </c>
+      <c r="AQ3">
+        <v>0.3834808259587021</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ålandsbanken Abp (HLSE:ALBAV)</t>
+          <t>Nordea Bank Abp (OM:NDA SE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +853,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07490000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="E4">
-        <v>0.121</v>
+        <v>0.0984</v>
+      </c>
+      <c r="F4">
+        <v>0.116</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,85 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>35.4</v>
+        <v>5407.5</v>
       </c>
       <c r="L4">
-        <v>0.2054556006964596</v>
+        <v>0.4367402980252796</v>
       </c>
       <c r="M4">
-        <v>34.54</v>
+        <v>4656</v>
       </c>
       <c r="N4">
-        <v>0.05758586195398466</v>
+        <v>0.1069012862134995</v>
       </c>
       <c r="O4">
-        <v>0.9757062146892655</v>
+        <v>0.8610263522884882</v>
       </c>
       <c r="P4">
-        <v>31.6</v>
+        <v>3071.5</v>
       </c>
       <c r="Q4">
-        <v>0.05268422807602535</v>
+        <v>0.07052132744947674</v>
       </c>
       <c r="R4">
-        <v>0.8926553672316385</v>
+        <v>0.5680073971336107</v>
       </c>
       <c r="S4">
-        <v>2.939999999999998</v>
+        <v>1584.5</v>
       </c>
       <c r="T4">
-        <v>0.0851187029530978</v>
+        <v>0.3403135738831615</v>
       </c>
       <c r="U4">
-        <v>552.3</v>
+        <v>63969.1</v>
       </c>
       <c r="V4">
-        <v>0.9208069356452151</v>
+        <v>1.468724026615114</v>
       </c>
       <c r="W4">
-        <v>0.09485530546623794</v>
+        <v>0.1777403068670374</v>
       </c>
       <c r="X4">
-        <v>0.1233984439245765</v>
+        <v>0.1508060465346924</v>
       </c>
       <c r="Y4">
-        <v>-0.02854313845833853</v>
+        <v>0.026934260332345</v>
       </c>
       <c r="Z4">
-        <v>0.09774222827320174</v>
+        <v>0.065156358948047</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07143053677294475</v>
+        <v>0.05736554434814577</v>
       </c>
       <c r="AC4">
-        <v>-0.07143053677294475</v>
+        <v>-0.05736554434814577</v>
       </c>
       <c r="AD4">
-        <v>1416.9</v>
+        <v>244358.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1416.9</v>
+        <v>244358.6</v>
       </c>
       <c r="AG4">
-        <v>864.6000000000001</v>
+        <v>180389.5</v>
       </c>
       <c r="AH4">
-        <v>0.7025834283730847</v>
+        <v>0.8487243359795049</v>
       </c>
       <c r="AI4">
-        <v>0.822440213605758</v>
+        <v>0.8837466501267618</v>
       </c>
       <c r="AJ4">
-        <v>0.5904124556132205</v>
+        <v>0.8055127248500404</v>
       </c>
       <c r="AK4">
-        <v>0.7386586928662966</v>
+        <v>0.8487563631025451</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fellow Pankki Oyj (HLSE:FELLOW)</t>
+          <t>Ålandsbanken Abp (HLSE:ALBAV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,113 +977,110 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.0819</v>
+      </c>
+      <c r="E5">
+        <v>0.135</v>
+      </c>
       <c r="G5">
-        <v>-0.6949924127465857</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-0.6949924127465857</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-1.987860394537178</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-1.987860394537178</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-8.58</v>
+        <v>43.6</v>
       </c>
       <c r="L5">
-        <v>-1.301972685887709</v>
+        <v>0.2174563591022444</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>37.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.07072243346007605</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.8532110091743119</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>27.6</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05247148288973384</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.6330275229357798</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>9.600000000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.2580645161290323</v>
       </c>
       <c r="U5">
-        <v>141</v>
+        <v>351.8</v>
       </c>
       <c r="V5">
-        <v>4.110787172011662</v>
+        <v>0.6688212927756654</v>
       </c>
       <c r="W5">
-        <v>-0.5329192546583851</v>
+        <v>0.1425302386400785</v>
       </c>
       <c r="X5">
-        <v>0.2277104026362627</v>
+        <v>0.09764622885505417</v>
       </c>
       <c r="Y5">
-        <v>-0.7606296572946478</v>
+        <v>0.0448840097850243</v>
       </c>
       <c r="Z5">
-        <v>0.2809036658141517</v>
+        <v>0.1712943186672362</v>
       </c>
       <c r="AA5">
-        <v>-0.5583972719522591</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07356561526529523</v>
+        <v>0.06085905729333261</v>
       </c>
       <c r="AC5">
-        <v>-0.6319628872175543</v>
+        <v>-0.06085905729333261</v>
       </c>
       <c r="AD5">
-        <v>233.8</v>
+        <v>1238.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>233.8</v>
+        <v>1238.4</v>
       </c>
       <c r="AG5">
-        <v>92.80000000000001</v>
+        <v>886.6000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.8720626631853785</v>
+        <v>0.7018816594876446</v>
       </c>
       <c r="AI5">
-        <v>0.8835978835978836</v>
+        <v>0.7868352500158842</v>
       </c>
       <c r="AJ5">
-        <v>0.7301337529504328</v>
+        <v>0.6276369814526406</v>
       </c>
       <c r="AK5">
-        <v>0.7508090614886732</v>
+        <v>0.7254725472547255</v>
       </c>
       <c r="AL5">
-        <v>0.613</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-4.186999999999999</v>
-      </c>
-      <c r="AN5">
-        <v>-18.12403100775194</v>
-      </c>
-      <c r="AO5">
-        <v>-21.37030995106036</v>
-      </c>
-      <c r="AP5">
-        <v>-7.193798449612403</v>
-      </c>
-      <c r="AQ5">
-        <v>3.128731788870313</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0819</v>
+        <v>0.0799</v>
       </c>
       <c r="E2">
-        <v>0.1167</v>
+        <v>0.312</v>
       </c>
       <c r="F2">
-        <v>0.116</v>
+        <v>-0.00672</v>
       </c>
       <c r="G2">
-        <v>-0.0005542860769938747</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-0.0005990351962931225</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001031451331365642</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>8.827321278215912e-05</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>5447</v>
+        <v>5616.8</v>
       </c>
       <c r="L2">
-        <v>0.4321781078422038</v>
+        <v>0.4247300444632649</v>
       </c>
       <c r="M2">
-        <v>4693.2</v>
+        <v>4201.4</v>
       </c>
       <c r="N2">
-        <v>0.1064290087761072</v>
+        <v>0.1106828701569329</v>
       </c>
       <c r="O2">
-        <v>0.8616118964567652</v>
+        <v>0.7480059820538384</v>
       </c>
       <c r="P2">
-        <v>3099.1</v>
+        <v>3618.1</v>
       </c>
       <c r="Q2">
-        <v>0.07027915731228881</v>
+        <v>0.0953162499440184</v>
       </c>
       <c r="R2">
-        <v>0.5689553882871305</v>
+        <v>0.6441568152684802</v>
       </c>
       <c r="S2">
-        <v>1594.1</v>
+        <v>583.2999999999997</v>
       </c>
       <c r="T2">
-        <v>0.3396616381147192</v>
+        <v>0.1388346741562336</v>
       </c>
       <c r="U2">
-        <v>64438.5</v>
+        <v>58706.2</v>
       </c>
       <c r="V2">
-        <v>1.461289883665555</v>
+        <v>1.546572740516717</v>
       </c>
       <c r="W2">
-        <v>0.1425302386400785</v>
+        <v>0.1747365015368151</v>
       </c>
       <c r="X2">
-        <v>0.1508060465346924</v>
+        <v>0.1638467568378134</v>
       </c>
       <c r="Y2">
-        <v>-0.008275807894613962</v>
+        <v>0.01088974469900172</v>
       </c>
       <c r="Z2">
-        <v>0.06587871053855517</v>
+        <v>0.06291655862923695</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06041816179158038</v>
+        <v>0.06129686292270316</v>
       </c>
       <c r="AC2">
-        <v>-0.05736554434814577</v>
+        <v>-0.06129686292270316</v>
       </c>
       <c r="AD2">
-        <v>245868.1</v>
+        <v>244966.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>245868.1</v>
+        <v>244966.5</v>
       </c>
       <c r="AG2">
-        <v>181429.6</v>
+        <v>186260.3</v>
       </c>
       <c r="AH2">
-        <v>0.8479230776393436</v>
+        <v>0.8658342446454083</v>
       </c>
       <c r="AI2">
-        <v>0.8832208299042269</v>
+        <v>0.8747307157097053</v>
       </c>
       <c r="AJ2">
-        <v>0.8044709581929582</v>
+        <v>0.8307062909866774</v>
       </c>
       <c r="AK2">
-        <v>0.8480467723856703</v>
+        <v>0.841505690071053</v>
       </c>
       <c r="AL2">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.39</v>
-      </c>
-      <c r="AN2">
-        <v>127392.7979274611</v>
-      </c>
-      <c r="AO2">
-        <v>0.3834808259587021</v>
-      </c>
-      <c r="AP2">
-        <v>94004.97409326426</v>
-      </c>
-      <c r="AQ2">
-        <v>0.3834808259587021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alisa Pankki Oyj (HLSE:ALISA)</t>
+          <t>Nordea Bank Abp (HLSE:NDA FI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,361 +713,111 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.139</v>
+        <v>0.0799</v>
+      </c>
+      <c r="E3">
+        <v>0.312</v>
+      </c>
+      <c r="F3">
+        <v>-0.00672</v>
       </c>
       <c r="G3">
-        <v>-0.3234259259259259</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-0.349537037037037</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.06018518518518518</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.06018518518518518</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>-4.1</v>
+        <v>5616.8</v>
       </c>
       <c r="L3">
-        <v>-0.1898148148148148</v>
+        <v>0.4247300444632649</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>4201.4</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1106828701569329</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.7480059820538384</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3618.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0953162499440184</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.6441568152684802</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>583.2999999999997</v>
+      </c>
+      <c r="T3">
+        <v>0.1388346741562336</v>
       </c>
       <c r="U3">
-        <v>117.6</v>
+        <v>58706.2</v>
       </c>
       <c r="V3">
-        <v>6.999999999999999</v>
+        <v>1.546572740516717</v>
       </c>
       <c r="W3">
-        <v>-0.1331168831168831</v>
+        <v>0.1747365015368151</v>
       </c>
       <c r="X3">
-        <v>0.322664595466133</v>
+        <v>0.1638467568378134</v>
       </c>
       <c r="Y3">
-        <v>-0.4557814785830161</v>
+        <v>0.01088974469900172</v>
       </c>
       <c r="Z3">
-        <v>0.1842688960928169</v>
+        <v>0.06291655862923695</v>
       </c>
       <c r="AA3">
-        <v>0.01109025763521583</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06041816179158038</v>
+        <v>0.06129686292270316</v>
       </c>
       <c r="AC3">
-        <v>-0.04932790415636455</v>
+        <v>-0.06129686292270316</v>
       </c>
       <c r="AD3">
-        <v>271.1</v>
+        <v>244966.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>271.1</v>
+        <v>244966.5</v>
       </c>
       <c r="AG3">
-        <v>153.5</v>
+        <v>186260.3</v>
       </c>
       <c r="AH3">
-        <v>0.9416464050017367</v>
+        <v>0.8658342446454083</v>
       </c>
       <c r="AI3">
-        <v>0.9042695130086725</v>
+        <v>0.8747307157097053</v>
       </c>
       <c r="AJ3">
-        <v>0.9013505578391074</v>
+        <v>0.8307062909866774</v>
       </c>
       <c r="AK3">
-        <v>0.8424807903402854</v>
+        <v>0.841505690071053</v>
       </c>
       <c r="AL3">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.39</v>
-      </c>
-      <c r="AN3">
-        <v>140.4663212435233</v>
-      </c>
-      <c r="AO3">
-        <v>0.3834808259587021</v>
-      </c>
-      <c r="AP3">
-        <v>79.5336787564767</v>
-      </c>
-      <c r="AQ3">
-        <v>0.3834808259587021</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nordea Bank Abp (OM:NDA SE)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0585</v>
-      </c>
-      <c r="E4">
-        <v>0.0984</v>
-      </c>
-      <c r="F4">
-        <v>0.116</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>5407.5</v>
-      </c>
-      <c r="L4">
-        <v>0.4367402980252796</v>
-      </c>
-      <c r="M4">
-        <v>4656</v>
-      </c>
-      <c r="N4">
-        <v>0.1069012862134995</v>
-      </c>
-      <c r="O4">
-        <v>0.8610263522884882</v>
-      </c>
-      <c r="P4">
-        <v>3071.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.07052132744947674</v>
-      </c>
-      <c r="R4">
-        <v>0.5680073971336107</v>
-      </c>
-      <c r="S4">
-        <v>1584.5</v>
-      </c>
-      <c r="T4">
-        <v>0.3403135738831615</v>
-      </c>
-      <c r="U4">
-        <v>63969.1</v>
-      </c>
-      <c r="V4">
-        <v>1.468724026615114</v>
-      </c>
-      <c r="W4">
-        <v>0.1777403068670374</v>
-      </c>
-      <c r="X4">
-        <v>0.1508060465346924</v>
-      </c>
-      <c r="Y4">
-        <v>0.026934260332345</v>
-      </c>
-      <c r="Z4">
-        <v>0.065156358948047</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.05736554434814577</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05736554434814577</v>
-      </c>
-      <c r="AD4">
-        <v>244358.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>244358.6</v>
-      </c>
-      <c r="AG4">
-        <v>180389.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.8487243359795049</v>
-      </c>
-      <c r="AI4">
-        <v>0.8837466501267618</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8055127248500404</v>
-      </c>
-      <c r="AK4">
-        <v>0.8487563631025451</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ålandsbanken Abp (HLSE:ALBAV)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0819</v>
-      </c>
-      <c r="E5">
-        <v>0.135</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>43.6</v>
-      </c>
-      <c r="L5">
-        <v>0.2174563591022444</v>
-      </c>
-      <c r="M5">
-        <v>37.2</v>
-      </c>
-      <c r="N5">
-        <v>0.07072243346007605</v>
-      </c>
-      <c r="O5">
-        <v>0.8532110091743119</v>
-      </c>
-      <c r="P5">
-        <v>27.6</v>
-      </c>
-      <c r="Q5">
-        <v>0.05247148288973384</v>
-      </c>
-      <c r="R5">
-        <v>0.6330275229357798</v>
-      </c>
-      <c r="S5">
-        <v>9.600000000000001</v>
-      </c>
-      <c r="T5">
-        <v>0.2580645161290323</v>
-      </c>
-      <c r="U5">
-        <v>351.8</v>
-      </c>
-      <c r="V5">
-        <v>0.6688212927756654</v>
-      </c>
-      <c r="W5">
-        <v>0.1425302386400785</v>
-      </c>
-      <c r="X5">
-        <v>0.09764622885505417</v>
-      </c>
-      <c r="Y5">
-        <v>0.0448840097850243</v>
-      </c>
-      <c r="Z5">
-        <v>0.1712943186672362</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06085905729333261</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06085905729333261</v>
-      </c>
-      <c r="AD5">
-        <v>1238.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1238.4</v>
-      </c>
-      <c r="AG5">
-        <v>886.6000000000001</v>
-      </c>
-      <c r="AH5">
-        <v>0.7018816594876446</v>
-      </c>
-      <c r="AI5">
-        <v>0.7868352500158842</v>
-      </c>
-      <c r="AJ5">
-        <v>0.6276369814526406</v>
-      </c>
-      <c r="AK5">
-        <v>0.7254725472547255</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0799</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>0.312</v>
+        <v>0.242</v>
       </c>
       <c r="F2">
-        <v>-0.00672</v>
+        <v>0.5656399999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.00055666711128896</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0005068694144324396</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.000656558919864242</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.0005633750158252684</v>
       </c>
       <c r="K2">
-        <v>5616.8</v>
+        <v>5677.110000000001</v>
       </c>
       <c r="L2">
-        <v>0.4247300444632649</v>
+        <v>0.4206949446445245</v>
       </c>
       <c r="M2">
-        <v>4201.4</v>
+        <v>4245.4</v>
       </c>
       <c r="N2">
-        <v>0.1106828701569329</v>
+        <v>0.1102025771215566</v>
       </c>
       <c r="O2">
-        <v>0.7480059820538384</v>
+        <v>0.747810065332537</v>
       </c>
       <c r="P2">
-        <v>3618.1</v>
+        <v>3662.1</v>
       </c>
       <c r="Q2">
-        <v>0.0953162499440184</v>
+        <v>0.09506120923278198</v>
       </c>
       <c r="R2">
-        <v>0.6441568152684802</v>
+        <v>0.6450641259373167</v>
       </c>
       <c r="S2">
         <v>583.2999999999997</v>
       </c>
       <c r="T2">
-        <v>0.1388346741562336</v>
+        <v>0.1373957695387949</v>
       </c>
       <c r="U2">
-        <v>58706.2</v>
+        <v>59290.2</v>
       </c>
       <c r="V2">
-        <v>1.546572740516717</v>
+        <v>1.539061769928044</v>
       </c>
       <c r="W2">
         <v>0.1747365015368151</v>
       </c>
       <c r="X2">
-        <v>0.1638467568378134</v>
+        <v>0.1637854648881576</v>
       </c>
       <c r="Y2">
-        <v>0.01088974469900172</v>
+        <v>0.01095103664865749</v>
       </c>
       <c r="Z2">
-        <v>0.06291655862923695</v>
+        <v>0.06377761346501355</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06129686292270316</v>
+        <v>0.06167875669513626</v>
       </c>
       <c r="AC2">
-        <v>-0.06129686292270316</v>
+        <v>-0.06128863964198043</v>
       </c>
       <c r="AD2">
-        <v>244966.5</v>
+        <v>246521.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>244966.5</v>
+        <v>246521.7</v>
       </c>
       <c r="AG2">
-        <v>186260.3</v>
+        <v>187231.5</v>
       </c>
       <c r="AH2">
-        <v>0.8658342446454083</v>
+        <v>0.8648509552692152</v>
       </c>
       <c r="AI2">
-        <v>0.8747307157097053</v>
+        <v>0.8741789558080266</v>
       </c>
       <c r="AJ2">
-        <v>0.8307062909866774</v>
+        <v>0.8293566789853253</v>
       </c>
       <c r="AK2">
-        <v>0.841505690071053</v>
+        <v>0.8406832095943892</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>11.2</v>
+      </c>
+      <c r="AN2">
+        <v>24850.97782258065</v>
+      </c>
+      <c r="AO2">
+        <v>0.7910714285714285</v>
+      </c>
+      <c r="AP2">
+        <v>18874.14314516129</v>
+      </c>
+      <c r="AQ2">
+        <v>0.7910714285714285</v>
       </c>
     </row>
     <row r="3">
@@ -704,120 +716,373 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Alisa Pankki Oyj (HLSE:ALISA)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.157</v>
+      </c>
+      <c r="F3">
+        <v>1.138</v>
+      </c>
+      <c r="G3">
+        <v>0.2487417218543046</v>
+      </c>
+      <c r="H3">
+        <v>0.2264900662251656</v>
+      </c>
+      <c r="I3">
+        <v>0.2933774834437086</v>
+      </c>
+      <c r="J3">
+        <v>0.2933774834437086</v>
+      </c>
+      <c r="K3">
+        <v>-2.09</v>
+      </c>
+      <c r="L3">
+        <v>-0.06920529801324503</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>386</v>
+      </c>
+      <c r="V3">
+        <v>15.19685039370079</v>
+      </c>
+      <c r="W3">
+        <v>-0.07282229965156795</v>
+      </c>
+      <c r="X3">
+        <v>0.3980956645659077</v>
+      </c>
+      <c r="Y3">
+        <v>-0.4709179642174757</v>
+      </c>
+      <c r="Z3">
+        <v>0.1719328209507543</v>
+      </c>
+      <c r="AA3">
+        <v>0.05044121833191004</v>
+      </c>
+      <c r="AB3">
+        <v>0.0647318790849641</v>
+      </c>
+      <c r="AC3">
+        <v>-0.01429066075305405</v>
+      </c>
+      <c r="AD3">
+        <v>552.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>552.5</v>
+      </c>
+      <c r="AG3">
+        <v>166.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.9560477591278769</v>
+      </c>
+      <c r="AI3">
+        <v>0.935489332881815</v>
+      </c>
+      <c r="AJ3">
+        <v>0.8676393955184992</v>
+      </c>
+      <c r="AK3">
+        <v>0.8137829912023461</v>
+      </c>
+      <c r="AL3">
+        <v>11.2</v>
+      </c>
+      <c r="AM3">
+        <v>11.2</v>
+      </c>
+      <c r="AN3">
+        <v>55.69556451612903</v>
+      </c>
+      <c r="AO3">
+        <v>0.7910714285714285</v>
+      </c>
+      <c r="AP3">
+        <v>16.78427419354839</v>
+      </c>
+      <c r="AQ3">
+        <v>0.7910714285714285</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Nordea Bank Abp (HLSE:NDA FI)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.0799</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0.312</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>-0.00672</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>5616.8</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>0.4247300444632649</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>4201.4</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.1106828701569329</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>0.7480059820538384</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>3618.1</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.0953162499440184</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>0.6441568152684802</v>
       </c>
-      <c r="S3">
+      <c r="S4">
         <v>583.2999999999997</v>
       </c>
-      <c r="T3">
+      <c r="T4">
         <v>0.1388346741562336</v>
       </c>
-      <c r="U3">
+      <c r="U4">
         <v>58706.2</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>1.546572740516717</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>0.1747365015368151</v>
       </c>
-      <c r="X3">
-        <v>0.1638467568378134</v>
-      </c>
-      <c r="Y3">
-        <v>0.01088974469900172</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.1637854648881576</v>
+      </c>
+      <c r="Y4">
+        <v>0.01095103664865749</v>
+      </c>
+      <c r="Z4">
         <v>0.06291655862923695</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06129686292270316</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06129686292270316</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06128863964198043</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06128863964198043</v>
+      </c>
+      <c r="AD4">
         <v>244966.5</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>244966.5</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>186260.3</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.8658342446454083</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.8747307157097053</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>0.8307062909866774</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>0.841505690071053</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ålandsbanken Abp (HLSE:ALBAV)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.109</v>
+      </c>
+      <c r="E5">
+        <v>0.172</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>62.4</v>
+      </c>
+      <c r="L5">
+        <v>0.26</v>
+      </c>
+      <c r="M5">
+        <v>44</v>
+      </c>
+      <c r="N5">
+        <v>0.08158724272204711</v>
+      </c>
+      <c r="O5">
+        <v>0.7051282051282052</v>
+      </c>
+      <c r="P5">
+        <v>44</v>
+      </c>
+      <c r="Q5">
+        <v>0.08158724272204711</v>
+      </c>
+      <c r="R5">
+        <v>0.7051282051282052</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>198</v>
+      </c>
+      <c r="V5">
+        <v>0.367142592249212</v>
+      </c>
+      <c r="W5">
+        <v>0.1853832442067736</v>
+      </c>
+      <c r="X5">
+        <v>0.09342112097636668</v>
+      </c>
+      <c r="Y5">
+        <v>0.09196212323040692</v>
+      </c>
+      <c r="Z5">
+        <v>0.1962066710268149</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06167875669513626</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06167875669513626</v>
+      </c>
+      <c r="AD5">
+        <v>1002.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1002.7</v>
+      </c>
+      <c r="AG5">
+        <v>804.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.6502594033722439</v>
+      </c>
+      <c r="AI5">
+        <v>0.7344711397597422</v>
+      </c>
+      <c r="AJ5">
+        <v>0.5987351190476191</v>
+      </c>
+      <c r="AK5">
+        <v>0.6894276901987663</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
